--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20232.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
   <si>
     <t>Mat</t>
   </si>
@@ -109,13 +109,22 @@
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>BONOLA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
   </si>
   <si>
     <t>ROSAS</t>
@@ -127,73 +136,76 @@
     <t>SARMIENTO</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>SORIA</t>
+  </si>
+  <si>
+    <t>ATENOGENES</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>JUAN SEBASTIAN</t>
   </si>
   <si>
-    <t>ANGEL NAIN</t>
-  </si>
-  <si>
-    <t>ALDO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
+    <t>JOEL MIGUEL</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>JOSELYN</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
@@ -205,28 +217,25 @@
     <t>NEMESIO NAHIM</t>
   </si>
   <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>EVELYN JOHANA</t>
-  </si>
-  <si>
     <t>ZABDIEL</t>
   </si>
   <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>JOSE DAMIAN</t>
+  </si>
+  <si>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
 </sst>
 </file>
@@ -734,16 +743,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>81.58</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1004,16 +1013,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="H2">
+        <v>5.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1027,16 +1039,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>74.36</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1050,16 +1065,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>64.52</v>
+      </c>
+      <c r="H4">
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1073,16 +1091,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H5">
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1096,16 +1117,19 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>92.11</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1119,16 +1143,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>44.83</v>
+      </c>
+      <c r="H7">
+        <v>5.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1142,16 +1169,19 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>60.87</v>
+      </c>
+      <c r="H8">
+        <v>5.9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1165,16 +1195,19 @@
         <v>33</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1188,16 +1221,19 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>41.67</v>
+      </c>
+      <c r="H10">
+        <v>5.8</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1211,16 +1247,19 @@
         <v>26</v>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>53.85</v>
+      </c>
+      <c r="H11">
+        <v>5.9</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1234,16 +1273,19 @@
         <v>32</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H12">
+        <v>7.1</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1257,16 +1299,19 @@
         <v>15</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H13">
+        <v>6.7</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1280,16 +1325,19 @@
         <v>25</v>
       </c>
       <c r="D14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H14">
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1402,7 @@
         <v>40</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1371,16 +1419,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>76.92</v>
+        <v>74.36</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1406,7 +1454,7 @@
         <v>64.52</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1432,7 +1480,7 @@
         <v>75</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1449,16 +1497,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>92.11</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1475,16 +1523,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7">
-        <v>37.93</v>
+        <v>44.83</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1501,16 +1549,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>65.22</v>
+        <v>60.87</v>
       </c>
       <c r="H8">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1536,7 +1584,7 @@
         <v>66.67</v>
       </c>
       <c r="H9">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1553,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="H10">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1579,13 +1627,13 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>65.38</v>
+        <v>53.85</v>
       </c>
       <c r="H11">
         <v>6.1</v>
@@ -1605,16 +1653,16 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12">
-        <v>78.13</v>
+        <v>75</v>
       </c>
       <c r="H12">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1640,7 +1688,7 @@
         <v>80</v>
       </c>
       <c r="H13">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1657,13 +1705,13 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H14">
         <v>7</v>
@@ -1676,7 +1724,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1717,7 +1765,7 @@
         <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1731,7 +1779,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920080</v>
+        <v>23330051920024</v>
       </c>
       <c r="B3" t="s">
         <v>30</v>
@@ -1740,13 +1788,13 @@
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1754,7 +1802,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920114</v>
+        <v>23330051920230</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
@@ -1763,13 +1811,13 @@
         <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1777,22 +1825,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920005</v>
+        <v>23330051920247</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1800,22 +1848,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920021</v>
+        <v>23330051920160</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1823,22 +1871,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920022</v>
+        <v>23330051920161</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1846,16 +1894,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920023</v>
+        <v>21330051920379</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1869,22 +1917,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920314</v>
+        <v>21330051920021</v>
       </c>
       <c r="B9" t="s">
         <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1892,16 +1940,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920379</v>
+        <v>21330051920022</v>
       </c>
       <c r="B10" t="s">
         <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1910,90 +1958,90 @@
         <v>19</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920191</v>
+        <v>21330051920023</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920075</v>
+        <v>21330051920125</v>
       </c>
       <c r="B12" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920125</v>
+        <v>21330051920031</v>
       </c>
       <c r="B13" t="s">
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920036</v>
+        <v>21330051920046</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -2002,27 +2050,27 @@
         <v>22</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920041</v>
+        <v>21330051920010</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
         <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2030,24 +2078,70 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920057</v>
+        <v>20330051920022</v>
       </c>
       <c r="B16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>21330051920028</v>
+      </c>
+      <c r="B17" t="s">
         <v>43</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>54</v>
       </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16">
+      <c r="D17" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>21330051920102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20232.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="99">
   <si>
     <t>Mat</t>
   </si>
@@ -106,136 +106,214 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>AMARO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ESPIRITU</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>DAMIAN</t>
   </si>
   <si>
     <t>MIXCOA</t>
   </si>
   <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>SORIA</t>
   </si>
   <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
-  </si>
-  <si>
-    <t>JOEL MIGUEL</t>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
   </si>
   <si>
     <t>JAIRO</t>
   </si>
   <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>JESUS JAREF</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>JAZIEL</t>
+  </si>
+  <si>
+    <t>ALEX URIEL</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>EVELYN JOHANA</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -1393,13 +1471,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="H2">
         <v>6.1</v>
@@ -1419,13 +1497,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
         <v>7.3</v>
@@ -1445,16 +1523,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>64.52</v>
+        <v>77.42</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1480,7 +1558,7 @@
         <v>75</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1497,16 +1575,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>92.11</v>
+        <v>86.84</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1523,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>44.83</v>
+        <v>65.52</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1549,16 +1627,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G8">
-        <v>60.87</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1601,16 +1679,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>41.67</v>
+        <v>66.67</v>
       </c>
       <c r="H10">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1627,16 +1705,16 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G11">
-        <v>53.85</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H11">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1662,7 +1740,7 @@
         <v>75</v>
       </c>
       <c r="H12">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1679,16 +1757,16 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>80</v>
+        <v>93.33</v>
       </c>
       <c r="H13">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1705,16 +1783,16 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1724,7 +1802,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1756,16 +1834,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920008</v>
+        <v>23330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1779,16 +1857,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920024</v>
+        <v>23330051920017</v>
       </c>
       <c r="B3" t="s">
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1802,22 +1880,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920230</v>
+        <v>23330051920321</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1825,22 +1903,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920247</v>
+        <v>23330051920022</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1848,22 +1926,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920160</v>
+        <v>23330051920112</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1871,22 +1949,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920161</v>
+        <v>23330051920230</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1894,22 +1972,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920379</v>
+        <v>23330051920229</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1917,22 +1995,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920021</v>
+        <v>23330051920342</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1940,22 +2018,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920022</v>
+        <v>23330051920164</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1963,22 +2041,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920023</v>
+        <v>23330051920313</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1986,22 +2064,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920125</v>
+        <v>23330051920191</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -2009,22 +2087,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920031</v>
+        <v>23330051920357</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -2032,22 +2110,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920046</v>
+        <v>23330051920280</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -2055,93 +2133,369 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920010</v>
+        <v>23330051920303</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920022</v>
+        <v>23330051920181</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920028</v>
+        <v>22330051920007</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920102</v>
+        <v>23330051920039</v>
       </c>
       <c r="B18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920212</v>
+      </c>
+      <c r="B19" t="s">
         <v>44</v>
       </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920116</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>21330051920109</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" t="s">
         <v>9</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F21" t="s">
         <v>20</v>
       </c>
-      <c r="G18">
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920366</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920367</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>21330051920021</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920191</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>21330051920071</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>21330051920075</v>
+      </c>
+      <c r="B27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>21330051920078</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>21330051920260</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>21330051920080</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20232.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="122">
   <si>
     <t>Mat</t>
   </si>
@@ -106,6 +106,42 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
@@ -139,15 +175,9 @@
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>LOBATO</t>
   </si>
   <si>
@@ -157,9 +187,6 @@
     <t>AMARO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -175,7 +202,31 @@
     <t>ESPIRITU</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>VOTE</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
   </si>
   <si>
     <t>VENTURA</t>
@@ -199,15 +250,9 @@
     <t>VALIENTE</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>RIOS</t>
-  </si>
-  <si>
     <t>DAMIAN</t>
   </si>
   <si>
@@ -217,9 +262,6 @@
     <t>VILLA</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>SORIA</t>
   </si>
   <si>
@@ -229,7 +271,40 @@
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
+    <t>HERSON</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>KEVIN IVAN</t>
+  </si>
+  <si>
+    <t>ANGEL JESUS</t>
+  </si>
+  <si>
+    <t>NOHEMI ANGELICA</t>
+  </si>
+  <si>
+    <t>CAMILO</t>
+  </si>
+  <si>
+    <t>KAREN AMERICA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>RAFAEL FELIPE</t>
@@ -271,9 +346,6 @@
     <t>ANGEL ABRAHAM</t>
   </si>
   <si>
-    <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
     <t>JESUS JAREF</t>
   </si>
   <si>
@@ -287,9 +359,6 @@
   </si>
   <si>
     <t>ISAAC</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
   </si>
   <si>
     <t>ELI ANTONIO</t>
@@ -1802,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1834,16 +1903,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920006</v>
+        <v>23330051920016</v>
       </c>
       <c r="B2" t="s">
         <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1857,16 +1926,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920017</v>
+        <v>23330051920025</v>
       </c>
       <c r="B3" t="s">
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1880,22 +1949,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920321</v>
+        <v>23330051920113</v>
       </c>
       <c r="B4" t="s">
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1903,22 +1972,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920022</v>
+        <v>23330051920233</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1926,22 +1995,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920112</v>
+        <v>23330051920264</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1949,16 +2018,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920230</v>
+        <v>23330051920267</v>
       </c>
       <c r="B7" t="s">
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1972,22 +2041,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920229</v>
+        <v>23330051920162</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1995,22 +2064,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920342</v>
+        <v>23330051920216</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -2018,22 +2087,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920164</v>
+        <v>23330051920303</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2041,22 +2110,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920313</v>
+        <v>22330061460232</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -2064,22 +2133,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920191</v>
+        <v>23330051920142</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -2087,22 +2156,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920357</v>
+        <v>21330051920109</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -2110,206 +2179,206 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920280</v>
+        <v>23330051920006</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920303</v>
+        <v>23330051920017</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920181</v>
+        <v>23330051920321</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920007</v>
+        <v>23330051920022</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920039</v>
+        <v>23330051920112</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920212</v>
+        <v>23330051920230</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920116</v>
+        <v>23330051920229</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920109</v>
+        <v>23330051920342</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920366</v>
+        <v>23330051920164</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2317,22 +2386,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920367</v>
+        <v>23330051920313</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2340,22 +2409,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920021</v>
+        <v>23330051920191</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2363,22 +2432,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920191</v>
+        <v>23330051920357</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2386,22 +2455,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920071</v>
+        <v>23330051920280</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2409,22 +2478,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920075</v>
+        <v>23330051920181</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2432,22 +2501,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920078</v>
+        <v>22330051920007</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2455,22 +2524,22 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920260</v>
+        <v>23330051920039</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2478,24 +2547,254 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
+        <v>23330051920212</v>
+      </c>
+      <c r="B30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>23330051920116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920366</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>114</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920367</v>
+      </c>
+      <c r="B33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>21330051920021</v>
+      </c>
+      <c r="B34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" t="s">
+        <v>81</v>
+      </c>
+      <c r="D34" t="s">
+        <v>115</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" t="s">
+        <v>19</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920191</v>
+      </c>
+      <c r="B35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>21330051920071</v>
+      </c>
+      <c r="B36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" t="s">
+        <v>117</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>21330051920075</v>
+      </c>
+      <c r="B37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>21330051920078</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>119</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>21330051920260</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" t="s">
+        <v>120</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
         <v>21330051920080</v>
       </c>
-      <c r="B30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" t="s">
         <v>9</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F40" t="s">
         <v>20</v>
       </c>
-      <c r="G30">
+      <c r="G40">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20232.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20232.xlsx
@@ -130,51 +130,51 @@
     <t>CARRERA</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MONTERD</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TELLO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>VIVANCO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -220,39 +220,39 @@
     <t>CERON</t>
   </si>
   <si>
+    <t>VOTE</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>RIOS</t>
   </si>
   <si>
-    <t>VOTE</t>
-  </si>
-  <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>DAMIAN</t>
   </si>
   <si>
@@ -295,55 +295,55 @@
     <t>ANGEL JESUS</t>
   </si>
   <si>
+    <t>CAMILO</t>
+  </si>
+  <si>
+    <t>KAREN AMERICA</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>MARGARITA</t>
+  </si>
+  <si>
+    <t>JAIRO</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>ANGEL ABRAHAM</t>
+  </si>
+  <si>
     <t>NOHEMI ANGELICA</t>
-  </si>
-  <si>
-    <t>CAMILO</t>
-  </si>
-  <si>
-    <t>KAREN AMERICA</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>RAFAEL FELIPE</t>
-  </si>
-  <si>
-    <t>ANGEL YAMIL</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>JAIRO</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MONICA</t>
-  </si>
-  <si>
-    <t>LUIS AARON</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>ANGEL ABRAHAM</t>
   </si>
   <si>
     <t>JESUS JAREF</t>
@@ -2024,7 +2024,7 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>89</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920303</v>
+        <v>22330061460232</v>
       </c>
       <c r="B10" t="s">
         <v>37</v>
@@ -2102,7 +2102,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330061460232</v>
+        <v>23330051920142</v>
       </c>
       <c r="B11" t="s">
         <v>38</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920142</v>
+        <v>21330051920109</v>
       </c>
       <c r="B12" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
         <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -2156,36 +2156,36 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920109</v>
+        <v>23330051920006</v>
       </c>
       <c r="B13" t="s">
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
         <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920006</v>
+        <v>23330051920017</v>
       </c>
       <c r="B14" t="s">
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
         <v>96</v>
@@ -2202,7 +2202,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920017</v>
+        <v>23330051920321</v>
       </c>
       <c r="B15" t="s">
         <v>42</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920321</v>
+        <v>23330051920022</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
@@ -2248,13 +2248,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920022</v>
+        <v>23330051920112</v>
       </c>
       <c r="B17" t="s">
         <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
         <v>99</v>
@@ -2263,7 +2263,7 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -2271,13 +2271,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920112</v>
+        <v>23330051920230</v>
       </c>
       <c r="B18" t="s">
         <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
         <v>100</v>
@@ -2286,7 +2286,7 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2294,10 +2294,10 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920230</v>
+        <v>23330051920229</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>73</v>
@@ -2317,13 +2317,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920229</v>
+        <v>23330051920342</v>
       </c>
       <c r="B20" t="s">
         <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
         <v>102</v>
@@ -2332,7 +2332,7 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2340,13 +2340,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920342</v>
+        <v>23330051920164</v>
       </c>
       <c r="B21" t="s">
         <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
         <v>103</v>
@@ -2363,13 +2363,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920164</v>
+        <v>23330051920313</v>
       </c>
       <c r="B22" t="s">
         <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
         <v>104</v>
@@ -2386,13 +2386,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920313</v>
+        <v>23330051920191</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
         <v>105</v>
@@ -2401,7 +2401,7 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2409,13 +2409,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920191</v>
+        <v>23330051920357</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
         <v>106</v>
@@ -2432,13 +2432,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920357</v>
+        <v>23330051920280</v>
       </c>
       <c r="B25" t="s">
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
         <v>107</v>
@@ -2455,7 +2455,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23330051920280</v>
+        <v>23330051920303</v>
       </c>
       <c r="B26" t="s">
         <v>51</v>
@@ -2470,7 +2470,7 @@
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2507,7 +2507,7 @@
         <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" t="s">
         <v>110</v>
@@ -2576,7 +2576,7 @@
         <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31" t="s">
         <v>113</v>
@@ -2691,7 +2691,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" t="s">
         <v>117</v>
@@ -2734,7 +2734,7 @@
         <v>21330051920078</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" t="s">
         <v>32</v>
@@ -2757,7 +2757,7 @@
         <v>21330051920260</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
         <v>83</v>
@@ -2780,7 +2780,7 @@
         <v>21330051920080</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
         <v>61</v>
